--- a/AAII_Financials/Quarterly/GAMI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GAMI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
   <si>
     <t>GAMI</t>
   </si>
@@ -2531,26 +2531,26 @@
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
+      <c r="D58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2576,22 +2576,22 @@
         <v>79600</v>
       </c>
       <c r="E59" s="3">
-        <v>76300</v>
+        <v>75200</v>
       </c>
       <c r="F59" s="3">
-        <v>81900</v>
+        <v>80500</v>
       </c>
       <c r="G59" s="3">
-        <v>83400</v>
+        <v>83000</v>
       </c>
       <c r="H59" s="3">
-        <v>70600</v>
+        <v>69900</v>
       </c>
       <c r="I59" s="3">
-        <v>71400</v>
+        <v>70400</v>
       </c>
       <c r="J59" s="3">
-        <v>81600</v>
+        <v>80200</v>
       </c>
       <c r="K59" s="3">
         <v>95600</v>

--- a/AAII_Financials/Quarterly/GAMI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GAMI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
   <si>
     <t>GAMI</t>
   </si>
@@ -656,117 +656,137 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>56900</v>
+      </c>
+      <c r="E8" s="3">
+        <v>57300</v>
+      </c>
+      <c r="F8" s="3">
+        <v>59500</v>
+      </c>
+      <c r="G8" s="3">
         <v>59200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="H8" s="3">
         <v>59900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="I8" s="3">
         <v>61600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="J8" s="3">
         <v>61900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="K8" s="3">
         <v>65600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="L8" s="3">
         <v>69600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="M8" s="3">
         <v>81700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="N8" s="3">
         <v>75900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="O8" s="3">
         <v>75600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="P8" s="3">
         <v>67900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="Q8" s="3">
         <v>71300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="R8" s="3">
         <v>61300</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -774,81 +794,99 @@
         <v>2200</v>
       </c>
       <c r="E9" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F9" s="3">
         <v>2000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
+        <v>2200</v>
+      </c>
+      <c r="H9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I9" s="3">
         <v>2300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="J9" s="3">
         <v>1700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="K9" s="3">
         <v>400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="L9" s="3">
         <v>1300</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="N9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L9" s="3">
+      <c r="O9" s="3">
         <v>3000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="P9" s="3">
         <v>2500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="Q9" s="3">
         <v>1700</v>
       </c>
-      <c r="O9" s="3" t="s">
+      <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>54700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>54900</v>
+      </c>
+      <c r="F10" s="3">
+        <v>57500</v>
+      </c>
+      <c r="G10" s="3">
         <v>57000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="H10" s="3">
         <v>57900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="I10" s="3">
         <v>59300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="J10" s="3">
         <v>60200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="K10" s="3">
         <v>65200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="L10" s="3">
         <v>68300</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L10" s="3">
+      <c r="O10" s="3">
         <v>72600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="P10" s="3">
         <v>65400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="Q10" s="3">
         <v>69600</v>
       </c>
-      <c r="O10" s="3" t="s">
+      <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,8 +902,11 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -905,8 +946,17 @@
       <c r="O12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,19 +996,28 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="3">
+        <v>200</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="F14" s="3">
-        <v>300</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
@@ -966,8 +1025,8 @@
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
+      <c r="I14" s="3">
+        <v>300</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>5</v>
@@ -975,20 +1034,29 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,8 +1096,17 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,90 +1119,111 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>41500</v>
+      </c>
+      <c r="F17" s="3">
+        <v>42000</v>
+      </c>
+      <c r="G17" s="3">
         <v>42700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="H17" s="3">
         <v>43500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="I17" s="3">
         <v>44600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="J17" s="3">
         <v>43900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="K17" s="3">
         <v>37300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="L17" s="3">
         <v>43700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="M17" s="3">
         <v>52200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="N17" s="3">
         <v>35200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="O17" s="3">
         <v>50800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="P17" s="3">
         <v>45500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="Q17" s="3">
         <v>47700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="R17" s="3">
         <v>29400</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>15800</v>
+      </c>
+      <c r="F18" s="3">
+        <v>17500</v>
+      </c>
+      <c r="G18" s="3">
         <v>16500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="H18" s="3">
         <v>16400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="I18" s="3">
         <v>17000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="J18" s="3">
         <v>18000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="K18" s="3">
         <v>28300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="L18" s="3">
         <v>25900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="M18" s="3">
         <v>29500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="N18" s="3">
         <v>40700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="O18" s="3">
         <v>24800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="P18" s="3">
         <v>22400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="Q18" s="3">
         <v>23600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="R18" s="3">
         <v>31900</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,90 +1239,111 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E20" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F20" s="3">
+        <v>600</v>
+      </c>
+      <c r="G20" s="3">
         <v>3500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="H20" s="3">
         <v>2200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="I20" s="3">
         <v>3800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="J20" s="3">
         <v>-1800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="K20" s="3">
         <v>-4000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="L20" s="3">
         <v>-2600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="M20" s="3">
         <v>-13200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="N20" s="3">
         <v>-1200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="O20" s="3">
         <v>3100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="P20" s="3">
         <v>900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="Q20" s="3">
         <v>4500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="R20" s="3">
         <v>-8600</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
+      <c r="D21" s="3">
+        <v>20200</v>
       </c>
       <c r="E21" s="3">
-        <v>17700</v>
+        <v>22600</v>
       </c>
       <c r="F21" s="3">
+        <v>18400</v>
+      </c>
+      <c r="G21" s="3">
+        <v>20300</v>
+      </c>
+      <c r="H21" s="3">
+        <v>18900</v>
+      </c>
+      <c r="I21" s="3">
         <v>21200</v>
-      </c>
-      <c r="G21" s="3">
-        <v>16600</v>
-      </c>
-      <c r="H21" s="3">
-        <v>24900</v>
-      </c>
-      <c r="I21" s="3">
-        <v>22500</v>
       </c>
       <c r="J21" s="3">
         <v>16600</v>
       </c>
       <c r="K21" s="3">
+        <v>24900</v>
+      </c>
+      <c r="L21" s="3">
+        <v>22500</v>
+      </c>
+      <c r="M21" s="3">
+        <v>16600</v>
+      </c>
+      <c r="N21" s="3">
         <v>39700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="O21" s="3">
         <v>28200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="P21" s="3">
         <v>22700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="Q21" s="3">
         <v>28500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="R21" s="3">
         <v>23600</v>
       </c>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1238,116 +1357,143 @@
         <v>300</v>
       </c>
       <c r="G22" s="3">
+        <v>300</v>
+      </c>
+      <c r="H22" s="3">
+        <v>300</v>
+      </c>
+      <c r="I22" s="3">
+        <v>300</v>
+      </c>
+      <c r="J22" s="3">
         <v>600</v>
-      </c>
-      <c r="H22" s="3">
-        <v>800</v>
-      </c>
-      <c r="I22" s="3">
-        <v>800</v>
-      </c>
-      <c r="J22" s="3">
-        <v>800</v>
       </c>
       <c r="K22" s="3">
         <v>800</v>
       </c>
       <c r="L22" s="3">
+        <v>800</v>
+      </c>
+      <c r="M22" s="3">
+        <v>800</v>
+      </c>
+      <c r="N22" s="3">
+        <v>800</v>
+      </c>
+      <c r="O22" s="3">
         <v>600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="P22" s="3">
         <v>700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="Q22" s="3">
         <v>600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="R22" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>22000</v>
+      </c>
+      <c r="F23" s="3">
+        <v>17800</v>
+      </c>
+      <c r="G23" s="3">
         <v>19800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="H23" s="3">
         <v>18300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="I23" s="3">
         <v>20600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="J23" s="3">
         <v>15600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="K23" s="3">
         <v>23500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="L23" s="3">
         <v>22600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="M23" s="3">
         <v>15400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="N23" s="3">
         <v>38600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="O23" s="3">
         <v>27300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="P23" s="3">
         <v>22700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="Q23" s="3">
         <v>27500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="R23" s="3">
         <v>22600</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E24" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F24" s="3">
+        <v>4700</v>
+      </c>
+      <c r="G24" s="3">
         <v>5200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="H24" s="3">
         <v>2400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="I24" s="3">
         <v>-800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="J24" s="3">
         <v>6100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="K24" s="3">
         <v>6200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="L24" s="3">
         <v>5100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="M24" s="3">
         <v>4400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="N24" s="3">
         <v>9500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="O24" s="3">
         <v>10200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="P24" s="3">
         <v>6700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="Q24" s="3">
         <v>7800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="R24" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,90 +1533,117 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>16600</v>
+      </c>
+      <c r="F26" s="3">
+        <v>13100</v>
+      </c>
+      <c r="G26" s="3">
         <v>14600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="H26" s="3">
         <v>15900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="I26" s="3">
         <v>21400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="J26" s="3">
         <v>9400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="K26" s="3">
         <v>17300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="L26" s="3">
         <v>17500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="M26" s="3">
         <v>11000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="N26" s="3">
         <v>29200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="O26" s="3">
         <v>17100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="P26" s="3">
         <v>16000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="Q26" s="3">
         <v>19700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="R26" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>16600</v>
+      </c>
+      <c r="F27" s="3">
+        <v>13100</v>
+      </c>
+      <c r="G27" s="3">
         <v>14600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="H27" s="3">
         <v>15900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="I27" s="3">
         <v>21400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="J27" s="3">
         <v>9400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="K27" s="3">
         <v>17300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="L27" s="3">
         <v>17500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="M27" s="3">
         <v>11000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="N27" s="3">
         <v>29200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="O27" s="3">
         <v>17100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="P27" s="3">
         <v>16000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="Q27" s="3">
         <v>19700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="R27" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1683,17 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1733,17 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1783,17 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,90 +1833,117 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="G32" s="3">
         <v>-3500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="H32" s="3">
         <v>-2200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="I32" s="3">
         <v>-3800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="J32" s="3">
         <v>1800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="K32" s="3">
         <v>4000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="L32" s="3">
         <v>2600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="M32" s="3">
         <v>13200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="N32" s="3">
         <v>1200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="O32" s="3">
         <v>-3100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="P32" s="3">
         <v>-900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="Q32" s="3">
         <v>-4500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="R32" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E33" s="3">
+        <v>16600</v>
+      </c>
+      <c r="F33" s="3">
+        <v>13100</v>
+      </c>
+      <c r="G33" s="3">
         <v>14600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="H33" s="3">
         <v>15900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="I33" s="3">
         <v>21400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="J33" s="3">
         <v>9400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="K33" s="3">
         <v>17300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="L33" s="3">
         <v>17500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="M33" s="3">
         <v>11000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="N33" s="3">
         <v>29200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="O33" s="3">
         <v>17100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="P33" s="3">
         <v>16000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="Q33" s="3">
         <v>19700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="R33" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,95 +1983,122 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E35" s="3">
+        <v>16600</v>
+      </c>
+      <c r="F35" s="3">
+        <v>13100</v>
+      </c>
+      <c r="G35" s="3">
         <v>14600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="H35" s="3">
         <v>15900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="I35" s="3">
         <v>21400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="J35" s="3">
         <v>9400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="K35" s="3">
         <v>17300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="L35" s="3">
         <v>17500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="M35" s="3">
         <v>11000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="N35" s="3">
         <v>29200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="O35" s="3">
         <v>17100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="P35" s="3">
         <v>16000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="Q35" s="3">
         <v>19700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="R35" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +2114,11 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,49 +2134,61 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>65500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>61800</v>
+      </c>
+      <c r="F41" s="3">
+        <v>125200</v>
+      </c>
+      <c r="G41" s="3">
         <v>149200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="H41" s="3">
         <v>133300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="I41" s="3">
         <v>66400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="J41" s="3">
         <v>102500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="K41" s="3">
         <v>133900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="L41" s="3">
         <v>144400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="M41" s="3">
         <v>142000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="N41" s="3">
         <v>152600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="O41" s="3">
         <v>118200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="P41" s="3">
         <v>118900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="Q41" s="3">
         <v>33300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="R41" s="3">
         <v>20300</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1959,49 +2228,67 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>35900</v>
+        <v>9500</v>
       </c>
       <c r="E43" s="3">
+        <v>13500</v>
+      </c>
+      <c r="F43" s="3">
+        <v>12800</v>
+      </c>
+      <c r="G43" s="3">
+        <v>15700</v>
+      </c>
+      <c r="H43" s="3">
         <v>14400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="I43" s="3">
         <v>18600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="J43" s="3">
         <v>13500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="K43" s="3">
         <v>13500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="L43" s="3">
         <v>10300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="M43" s="3">
         <v>10600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="N43" s="3">
         <v>13700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="O43" s="3">
         <v>14200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="P43" s="3">
         <v>13600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="Q43" s="3">
         <v>15300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="R43" s="3">
         <v>16300</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2041,8 +2328,17 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2082,8 +2378,17 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2123,110 +2428,137 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>44500</v>
+        <v>158500</v>
       </c>
       <c r="E47" s="3">
-        <v>46300</v>
+        <v>145600</v>
       </c>
       <c r="F47" s="3">
-        <v>106400</v>
+        <v>96700</v>
       </c>
       <c r="G47" s="3">
-        <v>58900</v>
+        <v>47200</v>
       </c>
       <c r="H47" s="3">
         <v>46300</v>
       </c>
       <c r="I47" s="3">
+        <v>106400</v>
+      </c>
+      <c r="J47" s="3">
+        <v>58900</v>
+      </c>
+      <c r="K47" s="3">
+        <v>46300</v>
+      </c>
+      <c r="L47" s="3">
         <v>41500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="M47" s="3">
         <v>35800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="N47" s="3">
         <v>32900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="O47" s="3">
         <v>37400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="P47" s="3">
         <v>44300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="Q47" s="3">
         <v>95700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="R47" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>5</v>
+      <c r="D48" s="3">
+        <v>5200</v>
       </c>
       <c r="E48" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F48" s="3">
+        <v>5400</v>
+      </c>
+      <c r="G48" s="3">
+        <v>5900</v>
+      </c>
+      <c r="H48" s="3">
         <v>6000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="I48" s="3">
         <v>6400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="J48" s="3">
         <v>6400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="K48" s="3">
         <v>7100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="L48" s="3">
         <v>7600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="M48" s="3">
         <v>8200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="N48" s="3">
         <v>4000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="O48" s="3">
         <v>4300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="P48" s="3">
         <v>4400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="Q48" s="3">
         <v>5000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="R48" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>5</v>
+      <c r="D49" s="3">
+        <v>2600</v>
       </c>
       <c r="E49" s="3">
-        <v>2800</v>
+        <v>2600</v>
       </c>
       <c r="F49" s="3">
         <v>2800</v>
       </c>
       <c r="G49" s="3">
-        <v>3200</v>
+        <v>2800</v>
       </c>
       <c r="H49" s="3">
-        <v>3200</v>
+        <v>2800</v>
       </c>
       <c r="I49" s="3">
-        <v>3200</v>
+        <v>2800</v>
       </c>
       <c r="J49" s="3">
         <v>3200</v>
@@ -2246,8 +2578,17 @@
       <c r="O49" s="3">
         <v>3200</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>3200</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>3200</v>
+      </c>
+      <c r="R49" s="3">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2628,17 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,8 +2678,17 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2369,8 +2728,17 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,49 +2778,67 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>263800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>249400</v>
+      </c>
+      <c r="F54" s="3">
+        <v>262200</v>
+      </c>
+      <c r="G54" s="3">
         <v>241000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="H54" s="3">
         <v>226100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
         <v>223800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="J54" s="3">
         <v>205200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="K54" s="3">
         <v>224800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="L54" s="3">
         <v>230200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3">
         <v>231700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <v>236300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="O54" s="3">
         <v>207100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="P54" s="3">
         <v>213800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="Q54" s="3">
         <v>185400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="R54" s="3">
         <v>191200</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2854,11 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,131 +2874,161 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>5</v>
+      <c r="D57" s="3">
+        <v>500</v>
       </c>
       <c r="E57" s="3">
+        <v>600</v>
+      </c>
+      <c r="F57" s="3">
         <v>400</v>
       </c>
-      <c r="F57" s="3">
-        <v>2900</v>
-      </c>
       <c r="G57" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H57" s="3">
         <v>400</v>
       </c>
       <c r="I57" s="3">
+        <v>2900</v>
+      </c>
+      <c r="J57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
+        <v>400</v>
+      </c>
+      <c r="L57" s="3">
+        <v>400</v>
+      </c>
+      <c r="M57" s="3">
         <v>5200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="N57" s="3">
         <v>500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="O57" s="3">
         <v>2700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="P57" s="3">
         <v>400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="Q57" s="3">
         <v>3800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="R57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F58" s="3">
+        <v>400</v>
+      </c>
+      <c r="G58" s="3">
+        <v>700</v>
+      </c>
+      <c r="H58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J58" s="3">
+        <v>300</v>
+      </c>
+      <c r="K58" s="3">
+        <v>700</v>
+      </c>
+      <c r="L58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>800</v>
+      </c>
+      <c r="R58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E58" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F58" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G58" s="3">
-        <v>300</v>
-      </c>
-      <c r="H58" s="3">
-        <v>700</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>1400</v>
-      </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3">
-        <v>800</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>79600</v>
+        <v>72800</v>
       </c>
       <c r="E59" s="3">
+        <v>66400</v>
+      </c>
+      <c r="F59" s="3">
+        <v>91300</v>
+      </c>
+      <c r="G59" s="3">
+        <v>78600</v>
+      </c>
+      <c r="H59" s="3">
         <v>75200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="I59" s="3">
         <v>80500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="J59" s="3">
         <v>83000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="K59" s="3">
         <v>69900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="L59" s="3">
         <v>70400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="M59" s="3">
         <v>80200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="N59" s="3">
         <v>95600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="O59" s="3">
         <v>91100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="P59" s="3">
         <v>87500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="Q59" s="3">
         <v>69600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="R59" s="3">
         <v>74900</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2649,8 +3068,17 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2667,31 +3095,40 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>33700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="L61" s="3">
         <v>50900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="M61" s="3">
         <v>51000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="N61" s="3">
         <v>52100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="O61" s="3">
         <v>52200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="P61" s="3">
         <v>24200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="Q61" s="3">
         <v>24200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="R61" s="3">
         <v>24200</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2731,8 +3168,17 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +3218,17 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +3268,17 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,49 +3318,67 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>74500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>68500</v>
+      </c>
+      <c r="F66" s="3">
+        <v>92100</v>
+      </c>
+      <c r="G66" s="3">
         <v>79600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="H66" s="3">
         <v>76700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="I66" s="3">
         <v>84800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="J66" s="3">
         <v>83800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="K66" s="3">
         <v>104700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="L66" s="3">
         <v>122800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="M66" s="3">
         <v>137800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="N66" s="3">
         <v>148100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="O66" s="3">
         <v>146000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="P66" s="3">
         <v>112100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="Q66" s="3">
         <v>98500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="R66" s="3">
         <v>99400</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3394,11 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3438,17 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3488,17 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3035,8 +3538,17 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,49 +3588,67 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>5</v>
+      <c r="D72" s="3">
+        <v>542500</v>
       </c>
       <c r="E72" s="3">
+        <v>527700</v>
+      </c>
+      <c r="F72" s="3">
+        <v>512200</v>
+      </c>
+      <c r="G72" s="3">
+        <v>500100</v>
+      </c>
+      <c r="H72" s="3">
         <v>486500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="I72" s="3">
         <v>471600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="J72" s="3">
         <v>451300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="K72" s="3">
         <v>442900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="L72" s="3">
         <v>426700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="M72" s="3">
         <v>410300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="N72" s="3">
         <v>400500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="O72" s="3">
         <v>371800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="P72" s="3">
         <v>409800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="Q72" s="3">
         <v>394400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="R72" s="3">
         <v>399800</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3688,17 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3738,17 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,49 +3788,67 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>189300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>181000</v>
+      </c>
+      <c r="F76" s="3">
+        <v>170100</v>
+      </c>
+      <c r="G76" s="3">
         <v>161400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="H76" s="3">
         <v>149500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
         <v>139100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="J76" s="3">
         <v>121500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="K76" s="3">
         <v>120100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="L76" s="3">
         <v>107400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="M76" s="3">
         <v>93900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="N76" s="3">
         <v>88200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="O76" s="3">
         <v>61100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="P76" s="3">
         <v>101700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="Q76" s="3">
         <v>86900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="R76" s="3">
         <v>91700</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,95 +3888,122 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E81" s="3">
+        <v>16600</v>
+      </c>
+      <c r="F81" s="3">
+        <v>13100</v>
+      </c>
+      <c r="G81" s="3">
         <v>14600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="H81" s="3">
         <v>15900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="I81" s="3">
         <v>21400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="J81" s="3">
         <v>9400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="K81" s="3">
         <v>17300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="L81" s="3">
         <v>17500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="M81" s="3">
         <v>11000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="N81" s="3">
         <v>29200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="O81" s="3">
         <v>17100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="P81" s="3">
         <v>16000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="Q81" s="3">
         <v>19700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="R81" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,16 +4019,19 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>5</v>
+      <c r="D83" s="3">
+        <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>-1000</v>
+        <v>300</v>
       </c>
       <c r="F83" s="3">
         <v>300</v>
@@ -3444,31 +4040,40 @@
         <v>300</v>
       </c>
       <c r="H83" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="I83" s="3">
-        <v>-900</v>
+        <v>300</v>
       </c>
       <c r="J83" s="3">
         <v>300</v>
       </c>
       <c r="K83" s="3">
+        <v>600</v>
+      </c>
+      <c r="L83" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M83" s="3">
+        <v>300</v>
+      </c>
+      <c r="N83" s="3">
         <v>200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="O83" s="3">
         <v>300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="P83" s="3">
         <v>-600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="Q83" s="3">
         <v>300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="R83" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +4113,17 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +4163,17 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +4213,17 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +4263,17 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,49 +4313,67 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>5</v>
+      <c r="D89" s="3">
+        <v>20200</v>
       </c>
       <c r="E89" s="3">
-        <v>-74400</v>
+        <v>-12900</v>
       </c>
       <c r="F89" s="3">
+        <v>31500</v>
+      </c>
+      <c r="G89" s="3">
+        <v>18400</v>
+      </c>
+      <c r="H89" s="3">
+        <v>12400</v>
+      </c>
+      <c r="I89" s="3">
         <v>28900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="J89" s="3">
         <v>26400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="K89" s="3">
         <v>31400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="L89" s="3">
         <v>-81400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="M89" s="3">
         <v>6100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="N89" s="3">
         <v>35700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="O89" s="3">
         <v>17700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="P89" s="3">
         <v>-4100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="Q89" s="3">
         <v>3100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="R89" s="3">
         <v>16700</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,8 +4389,11 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3771,8 +4433,17 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4483,17 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,49 +4533,67 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>5</v>
+      <c r="D94" s="3">
+        <v>-9000</v>
       </c>
       <c r="E94" s="3">
-        <v>148400</v>
+        <v>-44700</v>
       </c>
       <c r="F94" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="G94" s="3">
+        <v>200</v>
+      </c>
+      <c r="H94" s="3">
+        <v>60600</v>
+      </c>
+      <c r="I94" s="3">
         <v>-60500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="J94" s="3">
         <v>-14300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="K94" s="3">
         <v>-13100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="L94" s="3">
         <v>-67500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="M94" s="3">
         <v>-4100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="N94" s="3">
         <v>1800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="O94" s="3">
         <v>10600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="P94" s="3">
         <v>114800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="Q94" s="3">
         <v>34900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="R94" s="3">
         <v>-52300</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,16 +4609,19 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="E96" s="3">
-        <v>3100</v>
+        <v>-1000</v>
       </c>
       <c r="F96" s="3">
         <v>-1000</v>
@@ -3929,31 +4630,40 @@
         <v>-1000</v>
       </c>
       <c r="H96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-2100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="L96" s="3">
         <v>3300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="M96" s="3">
         <v>-2200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="N96" s="3">
         <v>-500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="O96" s="3">
         <v>-1100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="P96" s="3">
         <v>25400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="Q96" s="3">
         <v>-24300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="R96" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4703,17 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4753,17 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,54 +4803,72 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>5</v>
+      <c r="D100" s="3">
+        <v>-7500</v>
       </c>
       <c r="E100" s="3">
-        <v>68500</v>
+        <v>-5800</v>
       </c>
       <c r="F100" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="I100" s="3">
         <v>-4500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="J100" s="3">
         <v>-43600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="K100" s="3">
         <v>-26500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="L100" s="3">
         <v>42600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="M100" s="3">
         <v>-12600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="N100" s="3">
         <v>-3100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="O100" s="3">
         <v>-28900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="P100" s="3">
         <v>27600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="Q100" s="3">
         <v>-24900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="R100" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>5</v>
+      <c r="D101" s="3">
+        <v>0</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
@@ -4157,45 +4903,63 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>5</v>
+      <c r="D102" s="3">
+        <v>3700</v>
       </c>
       <c r="E102" s="3">
-        <v>142500</v>
+        <v>-63400</v>
       </c>
       <c r="F102" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="G102" s="3">
+        <v>15900</v>
+      </c>
+      <c r="H102" s="3">
+        <v>66900</v>
+      </c>
+      <c r="I102" s="3">
         <v>-36100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="J102" s="3">
         <v>-31400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="K102" s="3">
         <v>-8100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="L102" s="3">
         <v>-106400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="M102" s="3">
         <v>-10600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="N102" s="3">
         <v>34400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="O102" s="3">
         <v>-700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="P102" s="3">
         <v>138400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="Q102" s="3">
         <v>13000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="R102" s="3">
         <v>-37800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GAMI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GAMI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
   <si>
     <t>GAMI</t>
   </si>
@@ -656,237 +656,250 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>57600</v>
+      </c>
+      <c r="E8" s="3">
         <v>56900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>57300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>59500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>59200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>59900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>61600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>61900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>65600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>69600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>81700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>75900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>75600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>67900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>71300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>61300</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1300</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="3">
         <v>3000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1700</v>
       </c>
-      <c r="R9" s="3" t="s">
+      <c r="S9" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>55600</v>
+      </c>
+      <c r="E10" s="3">
         <v>54700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>54900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>57500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>57000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>57900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>59300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>60200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>65200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>68300</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="3">
         <v>72600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>65400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>69600</v>
       </c>
-      <c r="R10" s="3" t="s">
+      <c r="S10" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,8 +918,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -955,8 +969,11 @@
       <c r="R12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,19 +1022,22 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>200</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
@@ -1025,11 +1045,11 @@
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>300</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
@@ -1043,8 +1063,8 @@
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1055,8 +1075,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1105,8 +1128,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,108 +1148,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E17" s="3">
         <v>41600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>41500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>42000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>42700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>43500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>44600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>43900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>37300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>43700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>52200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>35200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>50800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>45500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>47700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>29400</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E18" s="3">
         <v>15300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>15800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>17500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>16500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>16400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>17000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>18000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>28300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>25900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>29500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>40700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>24800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>22400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>23600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>31900</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,108 +1275,115 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E20" s="3">
         <v>4700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>6500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-13200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>4500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-8600</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E21" s="3">
         <v>20200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>22600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>18400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>20300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>18900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>21200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>16600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>24900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>22500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>16600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>39700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>28200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>22700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>28500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>23600</v>
       </c>
     </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1366,10 +1406,10 @@
         <v>300</v>
       </c>
       <c r="J22" s="3">
+        <v>300</v>
+      </c>
+      <c r="K22" s="3">
         <v>600</v>
-      </c>
-      <c r="K22" s="3">
-        <v>800</v>
       </c>
       <c r="L22" s="3">
         <v>800</v>
@@ -1381,119 +1421,128 @@
         <v>800</v>
       </c>
       <c r="O22" s="3">
+        <v>800</v>
+      </c>
+      <c r="P22" s="3">
         <v>600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E23" s="3">
         <v>19700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>22000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>17800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>19800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>18300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>20600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>15600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>23500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>22600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>15400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>38600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>27300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>22700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>27500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>22600</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E24" s="3">
         <v>3900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>9500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>10200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E26" s="3">
         <v>15800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>16600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>13100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>14600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>15900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>21400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>9400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>17300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>17500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>11000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>29200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>17100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>16000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>19700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E27" s="3">
         <v>15800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>16600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>13100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>14600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>15900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>21400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>9400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>17300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>17500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>11000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>29200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>17100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>16000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>19700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1742,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,108 +1909,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-6500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>13200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-4500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E33" s="3">
         <v>15800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>16600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>13100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>14600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>15900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>21400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>9400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>17300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>17500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>11000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>29200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>17100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>16000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>19700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E35" s="3">
         <v>15800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>16600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>13100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>14600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>15900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>21400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>9400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>17300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>17500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>11000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>29200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>17100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>16000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>19700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,58 +2223,62 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>76100</v>
+      </c>
+      <c r="E41" s="3">
         <v>65500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>61800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>125200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>149200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>133300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>66400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>102500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>133900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>144400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>142000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>152600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>118200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>118900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>33300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>20300</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2237,58 +2327,64 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E43" s="3">
         <v>9500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>13500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>15700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>14400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>18600</v>
-      </c>
-      <c r="J43" s="3">
-        <v>13500</v>
       </c>
       <c r="K43" s="3">
         <v>13500</v>
       </c>
       <c r="L43" s="3">
+        <v>13500</v>
+      </c>
+      <c r="M43" s="3">
         <v>10300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>13700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>14200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>15300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>16300</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2337,8 +2433,11 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2387,8 +2486,11 @@
       <c r="R45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2437,8 +2539,11 @@
       <c r="R46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2446,99 +2551,105 @@
         <v>158500</v>
       </c>
       <c r="E47" s="3">
+        <v>158500</v>
+      </c>
+      <c r="F47" s="3">
         <v>145600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>96700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>47200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>46300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>106400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>58900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>46300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>41500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>35800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>32900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>37400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>44300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>95700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5200</v>
+        <v>5900</v>
       </c>
       <c r="E48" s="3">
         <v>5200</v>
       </c>
       <c r="F48" s="3">
+        <v>5200</v>
+      </c>
+      <c r="G48" s="3">
         <v>5400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6000</v>
-      </c>
-      <c r="I48" s="3">
-        <v>6400</v>
       </c>
       <c r="J48" s="3">
         <v>6400</v>
       </c>
       <c r="K48" s="3">
+        <v>6400</v>
+      </c>
+      <c r="L48" s="3">
         <v>7100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2549,7 +2660,7 @@
         <v>2600</v>
       </c>
       <c r="F49" s="3">
-        <v>2800</v>
+        <v>2600</v>
       </c>
       <c r="G49" s="3">
         <v>2800</v>
@@ -2561,7 +2672,7 @@
         <v>2800</v>
       </c>
       <c r="J49" s="3">
-        <v>3200</v>
+        <v>2800</v>
       </c>
       <c r="K49" s="3">
         <v>3200</v>
@@ -2587,8 +2698,11 @@
       <c r="R49" s="3">
         <v>3200</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,8 +2804,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2737,8 +2857,11 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,58 +2910,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>273900</v>
+      </c>
+      <c r="E54" s="3">
         <v>263800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>249400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>262200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>241000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>226100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>223800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>205200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>224800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>230200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>231700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>236300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>207100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>213800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>185400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>191200</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,31 +3007,32 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400</v>
+      </c>
+      <c r="E57" s="3">
         <v>500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2900</v>
-      </c>
-      <c r="J57" s="3">
-        <v>400</v>
       </c>
       <c r="K57" s="3">
         <v>400</v>
@@ -2910,61 +3041,64 @@
         <v>400</v>
       </c>
       <c r="M57" s="3">
+        <v>400</v>
+      </c>
+      <c r="N57" s="3">
         <v>5200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>700</v>
+      </c>
+      <c r="E58" s="3">
         <v>1100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1400</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
@@ -2972,63 +3106,69 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>800</v>
       </c>
-      <c r="R58" s="3" t="s">
+      <c r="S58" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>80300</v>
+      </c>
+      <c r="E59" s="3">
         <v>72800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>66400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>91300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>78600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>75200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>80500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>83000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>69900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>70400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>80200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>95600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>91100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>87500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>69600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>74900</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3077,8 +3217,11 @@
       <c r="R60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3104,22 +3247,22 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>33700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>50900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>51000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>52100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>52200</v>
-      </c>
-      <c r="P61" s="3">
-        <v>24200</v>
       </c>
       <c r="Q61" s="3">
         <v>24200</v>
@@ -3127,8 +3270,11 @@
       <c r="R61" s="3">
         <v>24200</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>24200</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3177,8 +3323,11 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,58 +3482,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>81400</v>
+      </c>
+      <c r="E66" s="3">
         <v>74500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>68500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>92100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>79600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>76700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>84800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>83800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>104700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>122800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>137800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>148100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>146000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>112100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>98500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>99400</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3547,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,58 +3768,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>551500</v>
+      </c>
+      <c r="E72" s="3">
         <v>542500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>527700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>512200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>500100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>486500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>471600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>451300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>442900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>426700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>410300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>400500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>371800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>409800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>394400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>399800</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,58 +3980,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>192400</v>
+      </c>
+      <c r="E76" s="3">
         <v>189300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>181000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>170100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>161400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>149500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>139100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>121500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>120100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>107400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>93900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>88200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>61100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>101700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>86900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>91700</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E81" s="3">
         <v>15800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>16600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>13100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>14600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>15900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>21400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>9400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>17300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>17500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>11000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>29200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>17100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>16000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>19700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,8 +4220,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4031,7 +4230,7 @@
         <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
         <v>300</v>
@@ -4049,31 +4248,34 @@
         <v>300</v>
       </c>
       <c r="K83" s="3">
+        <v>300</v>
+      </c>
+      <c r="L83" s="3">
         <v>600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>-900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>-600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,58 +4536,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E89" s="3">
         <v>20200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-12900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>31500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>18400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>12400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>28900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>26400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>31400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-81400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>35700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>17700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>16700</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,8 +4612,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4442,8 +4663,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,58 +4769,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-44700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-51000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>60600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-60500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-67500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>1800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>10600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>114800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>34900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-52300</v>
       </c>
     </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,13 +4845,14 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1000</v>
+        <v>-5900</v>
       </c>
       <c r="E96" s="3">
         <v>-1000</v>
@@ -4639,31 +4873,34 @@
         <v>-1000</v>
       </c>
       <c r="K96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="L96" s="3">
         <v>-2100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>3300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>25400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-24300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,58 +5055,64 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-7500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-6000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-43600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-26500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>42600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-12600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-28900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>27600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-24900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4912,54 +5161,60 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E102" s="3">
         <v>3700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-63400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-24000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>15900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>66900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-36100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-31400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-106400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-10600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>34400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>138400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>13000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-37800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GAMI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GAMI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
   <si>
     <t>GAMI</t>
   </si>
@@ -656,250 +656,263 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>57500</v>
+      </c>
+      <c r="E8" s="3">
         <v>57600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>56900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>57300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>59500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>59200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>59900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>61600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>61900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>65600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>69600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>81700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>75900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>75600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>67900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>71300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>61300</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2000</v>
+        <v>22600</v>
       </c>
       <c r="E9" s="3">
-        <v>2200</v>
+        <v>29000</v>
       </c>
       <c r="F9" s="3">
-        <v>2400</v>
+        <v>28600</v>
       </c>
       <c r="G9" s="3">
-        <v>2000</v>
+        <v>27300</v>
       </c>
       <c r="H9" s="3">
-        <v>2200</v>
+        <v>28200</v>
       </c>
       <c r="I9" s="3">
-        <v>2000</v>
+        <v>28100</v>
       </c>
       <c r="J9" s="3">
+        <v>29200</v>
+      </c>
+      <c r="K9" s="3">
         <v>2300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1300</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3">
         <v>3000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1700</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>55600</v>
+        <v>35000</v>
       </c>
       <c r="E10" s="3">
-        <v>54700</v>
+        <v>28600</v>
       </c>
       <c r="F10" s="3">
-        <v>54900</v>
+        <v>28400</v>
       </c>
       <c r="G10" s="3">
-        <v>57500</v>
+        <v>30000</v>
       </c>
       <c r="H10" s="3">
-        <v>57000</v>
+        <v>31300</v>
       </c>
       <c r="I10" s="3">
-        <v>57900</v>
+        <v>31100</v>
       </c>
       <c r="J10" s="3">
+        <v>30700</v>
+      </c>
+      <c r="K10" s="3">
         <v>59300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>60200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>65200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>68300</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3">
         <v>72600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>65400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>69600</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -919,8 +932,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -972,8 +986,11 @@
       <c r="S12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,35 +1042,38 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-100</v>
       </c>
       <c r="F14" s="3">
-        <v>200</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
+        <v>-1600</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="H14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-1600</v>
       </c>
       <c r="J14" s="3">
+        <v>-600</v>
+      </c>
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1066,8 +1086,8 @@
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1078,31 +1098,34 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1131,8 +1154,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>35900</v>
+      </c>
+      <c r="E17" s="3">
         <v>42000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>41600</v>
       </c>
-      <c r="F17" s="3">
-        <v>41500</v>
-      </c>
       <c r="G17" s="3">
+        <v>41300</v>
+      </c>
+      <c r="H17" s="3">
         <v>42000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>42700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>43500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>44600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>43900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>37300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>43700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>52200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>35200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>50800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>45500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>47700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>29400</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>15600</v>
+        <v>21600</v>
       </c>
       <c r="E18" s="3">
+        <v>15700</v>
+      </c>
+      <c r="F18" s="3">
         <v>15300</v>
       </c>
-      <c r="F18" s="3">
-        <v>15800</v>
-      </c>
       <c r="G18" s="3">
+        <v>16000</v>
+      </c>
+      <c r="H18" s="3">
         <v>17500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>16500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>16400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>17000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>18000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>28300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>25900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>29500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>40700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>24800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>22400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>23600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>31900</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,114 +1309,121 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2900</v>
-      </c>
-      <c r="E20" s="3">
-        <v>4700</v>
-      </c>
-      <c r="F20" s="3">
-        <v>6500</v>
-      </c>
-      <c r="G20" s="3">
-        <v>600</v>
-      </c>
-      <c r="H20" s="3">
-        <v>3500</v>
-      </c>
-      <c r="I20" s="3">
-        <v>2200</v>
-      </c>
-      <c r="J20" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
         <v>3800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-13200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>4500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-8600</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>18700</v>
+        <v>16800</v>
       </c>
       <c r="E21" s="3">
-        <v>20200</v>
+        <v>15900</v>
       </c>
       <c r="F21" s="3">
-        <v>22600</v>
+        <v>15600</v>
       </c>
       <c r="G21" s="3">
-        <v>18400</v>
+        <v>16300</v>
       </c>
       <c r="H21" s="3">
-        <v>20300</v>
+        <v>17800</v>
       </c>
       <c r="I21" s="3">
-        <v>18900</v>
+        <v>16800</v>
       </c>
       <c r="J21" s="3">
+        <v>16700</v>
+      </c>
+      <c r="K21" s="3">
         <v>21200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>16600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>24900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>22500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>16600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>39700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>28200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>22700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>28500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>23600</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1409,10 +1449,10 @@
         <v>300</v>
       </c>
       <c r="K22" s="3">
+        <v>300</v>
+      </c>
+      <c r="L22" s="3">
         <v>600</v>
-      </c>
-      <c r="L22" s="3">
-        <v>800</v>
       </c>
       <c r="M22" s="3">
         <v>800</v>
@@ -1424,125 +1464,134 @@
         <v>800</v>
       </c>
       <c r="P22" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q22" s="3">
         <v>600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E23" s="3">
         <v>18200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>19700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>22000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>17800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>19800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>18300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>20600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>15600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>23500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>22600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>15400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>38600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>27300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>22700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>27500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>22600</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E24" s="3">
         <v>3200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>10200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E26" s="3">
         <v>15000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>15800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>16600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>13100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>14600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>15900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>21400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>9400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>17300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>17500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>11000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>29200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>17100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>16000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>19700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E27" s="3">
         <v>15000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>15800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>16600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>13100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>14600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>15900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>21400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>9400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>17300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>17500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>11000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>29200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>17100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>16000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>19700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1806,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,114 +1979,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-6500</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="J32" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
         <v>-3800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>13200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-4500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E33" s="3">
         <v>15000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>15800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>16600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>13100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>14600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>15900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>21400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>9400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>17300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>17500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>11000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>29200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>17100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>16000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>19700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E35" s="3">
         <v>15000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>15800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>16600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>13100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>14600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>15900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>21400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>9400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>17300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>17500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>11000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>29200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>17100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>16000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>19700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,78 +2310,82 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>102300</v>
+      </c>
+      <c r="E41" s="3">
         <v>76100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>65500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>61800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>125200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>149200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>133300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>66400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>102500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>133900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>144400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>142000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>152600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>118200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>118900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>33300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>20300</v>
       </c>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>99100</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>99100</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>99100</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>49200</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -2330,84 +2420,90 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>12100</v>
+        <v>21500</v>
       </c>
       <c r="E43" s="3">
-        <v>9500</v>
+        <v>21500</v>
       </c>
       <c r="F43" s="3">
-        <v>13500</v>
+        <v>20800</v>
       </c>
       <c r="G43" s="3">
-        <v>12800</v>
+        <v>26200</v>
       </c>
       <c r="H43" s="3">
-        <v>15700</v>
+        <v>21400</v>
       </c>
       <c r="I43" s="3">
-        <v>14400</v>
+        <v>21500</v>
       </c>
       <c r="J43" s="3">
+        <v>23000</v>
+      </c>
+      <c r="K43" s="3">
         <v>18600</v>
-      </c>
-      <c r="K43" s="3">
-        <v>13500</v>
       </c>
       <c r="L43" s="3">
         <v>13500</v>
       </c>
       <c r="M43" s="3">
+        <v>13500</v>
+      </c>
+      <c r="N43" s="3">
         <v>10300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>14200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>13600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>15300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>16300</v>
       </c>
     </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2436,31 +2532,34 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2489,31 +2588,34 @@
       <c r="S45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>222900</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>196700</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>185400</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>187000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>195700</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>170700</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>156300</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2542,61 +2644,67 @@
       <c r="S46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>158500</v>
+        <v>59600</v>
       </c>
       <c r="E47" s="3">
-        <v>158500</v>
+        <v>57100</v>
       </c>
       <c r="F47" s="3">
-        <v>145600</v>
+        <v>56500</v>
       </c>
       <c r="G47" s="3">
-        <v>96700</v>
+        <v>44000</v>
       </c>
       <c r="H47" s="3">
-        <v>47200</v>
+        <v>45100</v>
       </c>
       <c r="I47" s="3">
+        <v>44500</v>
+      </c>
+      <c r="J47" s="3">
+        <v>43200</v>
+      </c>
+      <c r="K47" s="3">
+        <v>106400</v>
+      </c>
+      <c r="L47" s="3">
+        <v>58900</v>
+      </c>
+      <c r="M47" s="3">
         <v>46300</v>
       </c>
-      <c r="J47" s="3">
-        <v>106400</v>
-      </c>
-      <c r="K47" s="3">
-        <v>58900</v>
-      </c>
-      <c r="L47" s="3">
-        <v>46300</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>41500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>35800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>32900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>37400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>44300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>95700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2604,52 +2712,55 @@
         <v>5900</v>
       </c>
       <c r="E48" s="3">
-        <v>5200</v>
+        <v>5000</v>
       </c>
       <c r="F48" s="3">
-        <v>5200</v>
+        <v>2600</v>
       </c>
       <c r="G48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H48" s="3">
         <v>5400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5900</v>
       </c>
-      <c r="I48" s="3">
-        <v>6000</v>
-      </c>
-      <c r="J48" s="3">
-        <v>6400</v>
+      <c r="J48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K48" s="3">
         <v>6400</v>
       </c>
       <c r="L48" s="3">
+        <v>6400</v>
+      </c>
+      <c r="M48" s="3">
         <v>7100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2663,7 +2774,7 @@
         <v>2600</v>
       </c>
       <c r="G49" s="3">
-        <v>2800</v>
+        <v>2600</v>
       </c>
       <c r="H49" s="3">
         <v>2800</v>
@@ -2672,10 +2783,10 @@
         <v>2800</v>
       </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>2800</v>
-      </c>
-      <c r="K49" s="3">
-        <v>3200</v>
       </c>
       <c r="L49" s="3">
         <v>3200</v>
@@ -2701,8 +2812,11 @@
       <c r="S49" s="3">
         <v>3200</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,31 +2924,34 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>6700</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>13800</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2860,8 +2980,11 @@
       <c r="S52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,61 +3036,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>301400</v>
+      </c>
+      <c r="E54" s="3">
         <v>273900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>263800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>249400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>262200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>241000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>226100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>223800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>205200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>224800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>230200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>231700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>236300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>207100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>213800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>185400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>191200</v>
       </c>
     </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,34 +3138,35 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>400</v>
-      </c>
-      <c r="E57" s="3">
-        <v>500</v>
+      <c r="D57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F57" s="3">
-        <v>600</v>
-      </c>
-      <c r="G57" s="3">
-        <v>400</v>
-      </c>
-      <c r="H57" s="3">
-        <v>300</v>
-      </c>
-      <c r="I57" s="3">
-        <v>400</v>
-      </c>
-      <c r="J57" s="3">
+        <v>800</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K57" s="3">
         <v>2900</v>
-      </c>
-      <c r="K57" s="3">
-        <v>400</v>
       </c>
       <c r="L57" s="3">
         <v>400</v>
@@ -3044,64 +3175,67 @@
         <v>400</v>
       </c>
       <c r="N57" s="3">
+        <v>400</v>
+      </c>
+      <c r="O57" s="3">
         <v>5200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E58" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="F58" s="3">
         <v>1500</v>
       </c>
       <c r="G58" s="3">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="H58" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="I58" s="3">
         <v>1100</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>1400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1400</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -3109,89 +3243,95 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>800</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>80300</v>
+        <v>48500</v>
       </c>
       <c r="E59" s="3">
-        <v>72800</v>
+        <v>100</v>
       </c>
       <c r="F59" s="3">
-        <v>66400</v>
+        <v>3500</v>
       </c>
       <c r="G59" s="3">
-        <v>91300</v>
-      </c>
-      <c r="H59" s="3">
-        <v>78600</v>
-      </c>
-      <c r="I59" s="3">
-        <v>75200</v>
+        <v>0</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J59" s="3">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3">
         <v>80500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>83000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>69900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>70400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>80200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>95600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>91100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>87500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>69600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>74900</v>
       </c>
     </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>140800</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>76700</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>70300</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>45200</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>86900</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>74700</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>76700</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -3220,28 +3360,31 @@
       <c r="S60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -3250,22 +3393,22 @@
         <v>0</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>33700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>50900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>51000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>52100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>52200</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>24200</v>
       </c>
       <c r="R61" s="3">
         <v>24200</v>
@@ -3273,31 +3416,34 @@
       <c r="S61" s="3">
         <v>24200</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>24200</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>20100</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3326,8 +3472,11 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,61 +3640,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>146100</v>
+      </c>
+      <c r="E66" s="3">
         <v>81400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>74500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>68500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>92100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>79600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>76700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>84800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>83800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>104700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>122800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>137800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>148100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>146000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>112100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>98500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>99400</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3718,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,61 +3942,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>132100</v>
+      </c>
+      <c r="E72" s="3">
         <v>551500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>542500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>527700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>512200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>500100</v>
       </c>
-      <c r="I72" s="3">
-        <v>486500</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K72" s="3">
         <v>471600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>451300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>442900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>426700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>410300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>400500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>371800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>409800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>394400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>399800</v>
       </c>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,61 +4166,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>155300</v>
+      </c>
+      <c r="E76" s="3">
         <v>192400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>189300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>181000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>170100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>161400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>149500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>139100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>121500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>120100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>107400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>93900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>88200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>61100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>101700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>86900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>91700</v>
       </c>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E81" s="3">
         <v>15000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>15800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>16600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>13100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>14600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>15900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>21400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>9400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>17300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>17500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>11000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>29200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>17100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>16000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>19700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,16 +4419,17 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F83" s="3">
         <v>300</v>
@@ -4251,31 +4450,34 @@
         <v>300</v>
       </c>
       <c r="L83" s="3">
+        <v>300</v>
+      </c>
+      <c r="M83" s="3">
         <v>600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>-900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>-600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E89" s="3">
         <v>21000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>20200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-12900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>31500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>18400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>12400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>28900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>26400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>31400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-81400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>35700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>17700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>16700</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,31 +4833,32 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -4666,8 +4887,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,61 +4999,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E94" s="3">
         <v>1400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-9000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-44700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-51000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>60600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-60500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-13100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-67500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>10600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>114800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>34900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-52300</v>
       </c>
     </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,61 +5079,65 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-5900</v>
+        <v>1000</v>
       </c>
       <c r="E96" s="3">
-        <v>-1000</v>
+        <v>5900</v>
       </c>
       <c r="F96" s="3">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="G96" s="3">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="H96" s="3">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="I96" s="3">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="J96" s="3">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="K96" s="3">
         <v>-1000</v>
       </c>
       <c r="L96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M96" s="3">
         <v>-2100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>3300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>25400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-24300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,61 +5301,67 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-11800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-6000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-43600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-26500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>42600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-12600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-28900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>27600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-24900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5164,57 +5413,63 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>26200</v>
+      </c>
+      <c r="E102" s="3">
         <v>10600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-63400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-24000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>15900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>66900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-36100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-31400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-8100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-106400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-10600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>34400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>138400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>13000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-37800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GAMI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GAMI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="92">
   <si>
     <t>GAMI</t>
   </si>
@@ -656,263 +656,275 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>59300</v>
+      </c>
+      <c r="E8" s="3">
         <v>57500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>57600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>56900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>57300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>59500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>59200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>59900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>61600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>61900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>65600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>69600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>81700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>75900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>75600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>67900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>71300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>61300</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E9" s="3">
         <v>22600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>29000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>28600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>27300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>28200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>28100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>29200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1300</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3">
         <v>3000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1700</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>32700</v>
+      </c>
+      <c r="E10" s="3">
         <v>35000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>28600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>28400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>30000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>31300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>31100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>30700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>59300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>60200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>65200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>68300</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3">
         <v>72600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>65400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>69600</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,8 +945,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -989,8 +1002,11 @@
       <c r="T12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,38 +1061,41 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E14" s="3">
         <v>-3400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-3300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>300</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1089,8 +1108,8 @@
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1101,8 +1120,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1116,7 +1138,7 @@
         <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H15" s="3">
         <v>300</v>
@@ -1128,7 +1150,7 @@
         <v>300</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1157,8 +1179,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1201,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E17" s="3">
         <v>35900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>42000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>41600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>41300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>42000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>42700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>43500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>44600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>43900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>37300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>43700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>52200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>35200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>50800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>45500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>47700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>29400</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E18" s="3">
         <v>21600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>15700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>15300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>16000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>17500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>16500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>16400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>17000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>18000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>28300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>25900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>29500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>40700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>24800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>22400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>23600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>31900</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,17 +1342,18 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3">
         <v>5000</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1336,94 +1369,100 @@
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>3800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-13200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>4500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-8600</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E21" s="3">
         <v>16800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>15900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>15600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>16300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>17800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>16800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>16700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>21200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>16600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>24900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>22500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>16600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>39700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>28200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>22700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>28500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>23600</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1452,10 +1491,10 @@
         <v>300</v>
       </c>
       <c r="L22" s="3">
+        <v>300</v>
+      </c>
+      <c r="M22" s="3">
         <v>600</v>
-      </c>
-      <c r="M22" s="3">
-        <v>800</v>
       </c>
       <c r="N22" s="3">
         <v>800</v>
@@ -1467,75 +1506,81 @@
         <v>800</v>
       </c>
       <c r="Q22" s="3">
+        <v>800</v>
+      </c>
+      <c r="R22" s="3">
         <v>600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E23" s="3">
         <v>22700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>18200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>19700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>22000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>17800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>19800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>18300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>20600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>15600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>23500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>22600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>15400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>38600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>27300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>22700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>27500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>22600</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1543,55 +1588,58 @@
         <v>5800</v>
       </c>
       <c r="E24" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F24" s="3">
         <v>3200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>9500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>10200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>6700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,8 +1694,11 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1655,55 +1706,58 @@
         <v>16800</v>
       </c>
       <c r="E26" s="3">
+        <v>16800</v>
+      </c>
+      <c r="F26" s="3">
         <v>15000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>15800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>16600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>13100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>14600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>15900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>21400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>17300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>17500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>11000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>29200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>17100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>16000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>19700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1711,55 +1765,58 @@
         <v>16800</v>
       </c>
       <c r="E27" s="3">
+        <v>16800</v>
+      </c>
+      <c r="F27" s="3">
         <v>15000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>15800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>16600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>13100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>14600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>15900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>21400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>9400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>17300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>17500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>11000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>29200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>17100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>16000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>19700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1871,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1930,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1989,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,17 +2048,20 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3">
         <v>-5000</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F32" s="3" t="s">
         <v>5</v>
       </c>
@@ -2008,38 +2077,41 @@
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>-3800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>13200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-4500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2047,55 +2119,58 @@
         <v>16800</v>
       </c>
       <c r="E33" s="3">
+        <v>16800</v>
+      </c>
+      <c r="F33" s="3">
         <v>15000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>15800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>16600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>13100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>14600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>15900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>21400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>9400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>17300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>17500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>11000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>29200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>17100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>16000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>19700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,8 +2225,11 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2159,116 +2237,122 @@
         <v>16800</v>
       </c>
       <c r="E35" s="3">
+        <v>16800</v>
+      </c>
+      <c r="F35" s="3">
         <v>15000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>15800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>16600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>13100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>14600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>15900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>21400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>9400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>17300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>17500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>11000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>29200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>17100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>16000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>19700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2373,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,69 +2396,73 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E41" s="3">
         <v>102300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>76100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>65500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>61800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>125200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>149200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>133300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>66400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>102500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>133900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>144400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>142000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>152600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>118200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>118900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>33300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>20300</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>99100</v>
+        <v>99200</v>
       </c>
       <c r="E42" s="3">
         <v>99100</v>
@@ -2382,14 +2471,14 @@
         <v>99100</v>
       </c>
       <c r="G42" s="3">
+        <v>99100</v>
+      </c>
+      <c r="H42" s="3">
         <v>99000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>49200</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -2423,64 +2512,70 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>21500</v>
+        <v>24300</v>
       </c>
       <c r="E43" s="3">
         <v>21500</v>
       </c>
       <c r="F43" s="3">
+        <v>21500</v>
+      </c>
+      <c r="G43" s="3">
         <v>20800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>26200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>21400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>21500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>23000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>18600</v>
-      </c>
-      <c r="L43" s="3">
-        <v>13500</v>
       </c>
       <c r="M43" s="3">
         <v>13500</v>
       </c>
       <c r="N43" s="3">
+        <v>13500</v>
+      </c>
+      <c r="O43" s="3">
         <v>10300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>14200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>15300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>16300</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2505,8 +2600,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2535,8 +2630,11 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2561,8 +2659,8 @@
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -2591,35 +2689,38 @@
       <c r="T45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>140800</v>
+      </c>
+      <c r="E46" s="3">
         <v>222900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>196700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>185400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>187000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>195700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>170700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>156300</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2647,125 +2748,134 @@
       <c r="T46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>66300</v>
+      </c>
+      <c r="E47" s="3">
         <v>59600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>57100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>56500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>44000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>45100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>44500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>43200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>106400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>58900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>46300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>41500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>35800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>32900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>37400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>44300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>95700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" s="3">
         <v>5900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5900</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K48" s="3">
-        <v>6400</v>
+      <c r="K48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L48" s="3">
         <v>6400</v>
       </c>
       <c r="M48" s="3">
+        <v>6400</v>
+      </c>
+      <c r="N48" s="3">
         <v>7100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
         <v>2600</v>
@@ -2777,19 +2887,19 @@
         <v>2600</v>
       </c>
       <c r="H49" s="3">
-        <v>2800</v>
+        <v>2600</v>
       </c>
       <c r="I49" s="3">
         <v>2800</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>2800</v>
-      </c>
-      <c r="L49" s="3">
-        <v>3200</v>
       </c>
       <c r="M49" s="3">
         <v>3200</v>
@@ -2815,8 +2925,11 @@
       <c r="T49" s="3">
         <v>3200</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2984,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,35 +3043,38 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E52" s="3">
         <v>2500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>13800</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
@@ -2983,8 +3102,11 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3161,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>224200</v>
+      </c>
+      <c r="E54" s="3">
         <v>301400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>273900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>263800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>249400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>262200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>241000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>226100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>223800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>205200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>224800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>230200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>231700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>236300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>207100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>213800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>185400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>191200</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3245,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,8 +3268,9 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3150,12 +3280,12 @@
       <c r="E57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F57" s="3">
+      <c r="F57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G57" s="3">
         <v>800</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3165,11 +3295,11 @@
       <c r="J57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L57" s="3">
         <v>2900</v>
-      </c>
-      <c r="L57" s="3">
-        <v>400</v>
       </c>
       <c r="M57" s="3">
         <v>400</v>
@@ -3178,67 +3308,70 @@
         <v>400</v>
       </c>
       <c r="O57" s="3">
+        <v>400</v>
+      </c>
+      <c r="P57" s="3">
         <v>5200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1100</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>1400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1400</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -3246,96 +3379,102 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>800</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>200</v>
+      </c>
+      <c r="E59" s="3">
         <v>48500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3500</v>
       </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>5</v>
+      <c r="H59" s="3">
+        <v>0</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K59" s="3">
+        <v>0</v>
+      </c>
+      <c r="L59" s="3">
         <v>80500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>83000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>69900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>70400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>80200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>95600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>91100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>87500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>69600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>74900</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>87600</v>
+      </c>
+      <c r="E60" s="3">
         <v>140800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>76700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>70300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>45200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>86900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>74700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>76700</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -3363,32 +3502,35 @@
       <c r="T60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>4800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4600</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -3396,22 +3538,22 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>33700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>50900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>51000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>52100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>52200</v>
-      </c>
-      <c r="R61" s="3">
-        <v>24200</v>
       </c>
       <c r="S61" s="3">
         <v>24200</v>
@@ -3419,34 +3561,37 @@
       <c r="T61" s="3">
         <v>24200</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>24200</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>400</v>
+      <c r="D62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E62" s="3">
         <v>400</v>
       </c>
       <c r="F62" s="3">
+        <v>400</v>
+      </c>
+      <c r="G62" s="3">
         <v>500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>20100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>300</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -3475,8 +3620,11 @@
       <c r="T62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3679,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3738,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3797,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>87600</v>
+      </c>
+      <c r="E66" s="3">
         <v>146100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>81400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>74500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>68500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>92100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>79600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>76700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>84800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>83800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>104700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>122800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>137800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>148100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>146000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>112100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>98500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>99400</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3881,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3938,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3997,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4056,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4115,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E72" s="3">
         <v>132100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>551500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>542500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>527700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>512200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>500100</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L72" s="3">
         <v>471600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>451300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>442900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>426700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>410300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>400500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>371800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>409800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>394400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>399800</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4233,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4292,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4351,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>136600</v>
+      </c>
+      <c r="E76" s="3">
         <v>155300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>192400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>189300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>181000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>170100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>161400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>149500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>139100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>121500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>120100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>107400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>93900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>88200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>61100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>101700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>86900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>91700</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,69 +4469,75 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4351,55 +4545,58 @@
         <v>16800</v>
       </c>
       <c r="E81" s="3">
+        <v>16800</v>
+      </c>
+      <c r="F81" s="3">
         <v>15000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>15800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>16600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>13100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>14600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>15900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>21400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>9400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>17300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>17500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>11000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>29200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>17100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>16000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>19700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,8 +4617,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4453,31 +4651,34 @@
         <v>300</v>
       </c>
       <c r="M83" s="3">
+        <v>300</v>
+      </c>
+      <c r="N83" s="3">
         <v>600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>-900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>-600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4733,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4792,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4851,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4910,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4969,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3">
         <v>27500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>21000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>20200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-12900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>31500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>18400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>12400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>28900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>26400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>31400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-81400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>35700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>17700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>16700</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,8 +5053,9 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4860,8 +5080,8 @@
       <c r="J91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -4890,8 +5110,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5169,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,64 +5228,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3">
         <v>2300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-44700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-51000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>60600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-60500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-14300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-13100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-67500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>10600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>114800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>34900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-52300</v>
       </c>
     </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,19 +5312,20 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3">
         <v>1000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>5900</v>
-      </c>
-      <c r="F96" s="3">
-        <v>1000</v>
       </c>
       <c r="G96" s="3">
         <v>1000</v>
@@ -5107,37 +5340,40 @@
         <v>1000</v>
       </c>
       <c r="K96" s="3">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="L96" s="3">
         <v>-1000</v>
       </c>
       <c r="M96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="N96" s="3">
         <v>-2100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>3300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>25400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-24300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5428,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5487,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,64 +5546,70 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-11800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-43600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-26500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>42600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-12600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-28900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>27600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-24900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5416,60 +5664,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>26200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>10600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-63400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-24000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>15900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>66900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-36100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-31400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-106400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-10600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>34400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>138400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>13000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-37800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GAMI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GAMI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
   <si>
     <t>GAMI</t>
   </si>
@@ -656,157 +656,164 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>57300</v>
+      </c>
+      <c r="E8" s="3">
         <v>59300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>57500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>57600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>56900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>57300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>59500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>59200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>59900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>61600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>61900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>65600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>69600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>81700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>75900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>75600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>67900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>71300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>61300</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -814,117 +821,123 @@
         <v>26600</v>
       </c>
       <c r="E9" s="3">
+        <v>28800</v>
+      </c>
+      <c r="F9" s="3">
         <v>22600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>29000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>28600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>27300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>28200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>28100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>29200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1300</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R9" s="3">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3">
         <v>3000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1700</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>32700</v>
+        <v>30700</v>
       </c>
       <c r="E10" s="3">
+        <v>30400</v>
+      </c>
+      <c r="F10" s="3">
         <v>35000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>28600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>28400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>30000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>31300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>31100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>30700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>59300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>60200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>65200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>68300</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3">
         <v>72600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>65400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>69600</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -946,8 +959,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1005,8 +1019,11 @@
       <c r="U12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1064,41 +1081,44 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-3400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-3300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>300</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1111,8 +1131,8 @@
       <c r="Q14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1123,8 +1143,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1141,7 +1164,7 @@
         <v>200</v>
       </c>
       <c r="H15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
         <v>300</v>
@@ -1153,7 +1176,7 @@
         <v>300</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1182,8 +1205,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1202,126 +1228,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>40100</v>
+        <v>38700</v>
       </c>
       <c r="E17" s="3">
+        <v>42100</v>
+      </c>
+      <c r="F17" s="3">
         <v>35900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>42000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>41600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>41300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>42000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>42700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>43500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>44600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>43900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>37300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>43700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>52200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>35200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>50800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>45500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>47700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>29400</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>19200</v>
+        <v>18600</v>
       </c>
       <c r="E18" s="3">
+        <v>17100</v>
+      </c>
+      <c r="F18" s="3">
         <v>21600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>15700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>15300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>16000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>17500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>16500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>16400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>17000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>18000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>28300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>25900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>29500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>40700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>24800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>22400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>23600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>31900</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1343,8 +1376,9 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1352,11 +1386,11 @@
         <v>5</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>5000</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1372,97 +1406,103 @@
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>3800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>4500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-8600</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>19400</v>
+        <v>18800</v>
       </c>
       <c r="E21" s="3">
+        <v>17300</v>
+      </c>
+      <c r="F21" s="3">
         <v>16800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>15900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>15600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>16300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>17800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>16800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>16700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>21200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>16600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>24900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>22500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>16600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>39700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>28200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>22700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>28500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>23600</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1494,10 +1534,10 @@
         <v>300</v>
       </c>
       <c r="M22" s="3">
+        <v>300</v>
+      </c>
+      <c r="N22" s="3">
         <v>600</v>
-      </c>
-      <c r="N22" s="3">
-        <v>800</v>
       </c>
       <c r="O22" s="3">
         <v>800</v>
@@ -1509,137 +1549,146 @@
         <v>800</v>
       </c>
       <c r="R22" s="3">
+        <v>800</v>
+      </c>
+      <c r="S22" s="3">
         <v>600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>20600</v>
+      </c>
+      <c r="F23" s="3">
+        <v>22700</v>
+      </c>
+      <c r="G23" s="3">
+        <v>18200</v>
+      </c>
+      <c r="H23" s="3">
+        <v>19700</v>
+      </c>
+      <c r="I23" s="3">
+        <v>22000</v>
+      </c>
+      <c r="J23" s="3">
+        <v>17800</v>
+      </c>
+      <c r="K23" s="3">
+        <v>19800</v>
+      </c>
+      <c r="L23" s="3">
+        <v>18300</v>
+      </c>
+      <c r="M23" s="3">
+        <v>20600</v>
+      </c>
+      <c r="N23" s="3">
+        <v>15600</v>
+      </c>
+      <c r="O23" s="3">
+        <v>23500</v>
+      </c>
+      <c r="P23" s="3">
         <v>22600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="Q23" s="3">
+        <v>15400</v>
+      </c>
+      <c r="R23" s="3">
+        <v>38600</v>
+      </c>
+      <c r="S23" s="3">
+        <v>27300</v>
+      </c>
+      <c r="T23" s="3">
         <v>22700</v>
       </c>
-      <c r="F23" s="3">
-        <v>18200</v>
-      </c>
-      <c r="G23" s="3">
-        <v>19700</v>
-      </c>
-      <c r="H23" s="3">
-        <v>22000</v>
-      </c>
-      <c r="I23" s="3">
-        <v>17800</v>
-      </c>
-      <c r="J23" s="3">
-        <v>19800</v>
-      </c>
-      <c r="K23" s="3">
-        <v>18300</v>
-      </c>
-      <c r="L23" s="3">
-        <v>20600</v>
-      </c>
-      <c r="M23" s="3">
-        <v>15600</v>
-      </c>
-      <c r="N23" s="3">
-        <v>23500</v>
-      </c>
-      <c r="O23" s="3">
+      <c r="U23" s="3">
+        <v>27500</v>
+      </c>
+      <c r="V23" s="3">
         <v>22600</v>
       </c>
-      <c r="P23" s="3">
-        <v>15400</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>38600</v>
-      </c>
-      <c r="R23" s="3">
-        <v>27300</v>
-      </c>
-      <c r="S23" s="3">
-        <v>22700</v>
-      </c>
-      <c r="T23" s="3">
-        <v>27500</v>
-      </c>
-      <c r="U23" s="3">
-        <v>22600</v>
-      </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E24" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F24" s="3">
         <v>5800</v>
       </c>
-      <c r="E24" s="3">
-        <v>5800</v>
-      </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>9500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>10200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>6700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>7800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1697,126 +1746,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>15300</v>
+      </c>
+      <c r="F26" s="3">
         <v>16800</v>
       </c>
-      <c r="E26" s="3">
-        <v>16800</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>15000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>15800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>16600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>13100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>14600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>15900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>21400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>9400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>17300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>17500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>11000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>29200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>17100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>16000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>19700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>15300</v>
+      </c>
+      <c r="F27" s="3">
         <v>16800</v>
       </c>
-      <c r="E27" s="3">
-        <v>16800</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>15000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>15800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>16600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>13100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>14600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>15900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>21400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>9400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>17300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>17500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>11000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>29200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>17100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>16000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>19700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1874,8 +1932,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1933,8 +1994,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1992,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2051,8 +2118,11 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2060,11 +2130,11 @@
         <v>5</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-5000</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G32" s="3" t="s">
         <v>5</v>
       </c>
@@ -2080,97 +2150,103 @@
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>-3800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>13200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-4500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>15300</v>
+      </c>
+      <c r="F33" s="3">
         <v>16800</v>
       </c>
-      <c r="E33" s="3">
-        <v>16800</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>15000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>15800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>16600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>13100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>14600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>15900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>21400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>9400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>17300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>17500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>11000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>29200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>17100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>16000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>19700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2228,131 +2304,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>15300</v>
+      </c>
+      <c r="F35" s="3">
         <v>16800</v>
       </c>
-      <c r="E35" s="3">
-        <v>16800</v>
-      </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>15000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>15800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>16600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>13100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>14600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>15900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>21400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>9400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>17300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>17500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>11000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>29200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>17100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>16000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>19700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2374,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2397,75 +2483,79 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>53600</v>
+      </c>
+      <c r="E41" s="3">
         <v>17300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>102300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>76100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>65500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>61800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>125200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>149200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>133300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>66400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>102500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>133900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>144400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>142000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>152600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>118200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>118900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>33300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>20300</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>49900</v>
+      </c>
+      <c r="E42" s="3">
         <v>99200</v>
-      </c>
-      <c r="E42" s="3">
-        <v>99100</v>
       </c>
       <c r="F42" s="3">
         <v>99100</v>
@@ -2474,14 +2564,14 @@
         <v>99100</v>
       </c>
       <c r="H42" s="3">
+        <v>99100</v>
+      </c>
+      <c r="I42" s="3">
         <v>99000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>49200</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -2515,67 +2605,73 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>24300</v>
+        <v>23100</v>
       </c>
       <c r="E43" s="3">
-        <v>21500</v>
+        <v>23600</v>
       </c>
       <c r="F43" s="3">
         <v>21500</v>
       </c>
       <c r="G43" s="3">
+        <v>21500</v>
+      </c>
+      <c r="H43" s="3">
         <v>20800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>26200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>21400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>21500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>23000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>18600</v>
-      </c>
-      <c r="M43" s="3">
-        <v>13500</v>
       </c>
       <c r="N43" s="3">
         <v>13500</v>
       </c>
       <c r="O43" s="3">
+        <v>13500</v>
+      </c>
+      <c r="P43" s="3">
         <v>10300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>13700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>14200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>13600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>15300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>16300</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2603,8 +2699,8 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2633,8 +2729,11 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2662,8 +2761,8 @@
       <c r="K45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
+      <c r="L45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -2692,38 +2791,41 @@
       <c r="U45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>140800</v>
+        <v>126600</v>
       </c>
       <c r="E46" s="3">
+        <v>140000</v>
+      </c>
+      <c r="F46" s="3">
         <v>222900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>196700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>185400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>187000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>195700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>170700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>156300</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2751,67 +2853,73 @@
       <c r="U46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>71900</v>
+      </c>
+      <c r="E47" s="3">
         <v>66300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>59600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>57100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>56500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>44000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>45100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>44500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>43200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>106400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>58900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>46300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>41500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>35800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>32900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>37400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>44300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>95700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2819,58 +2927,61 @@
         <v>5</v>
       </c>
       <c r="E48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F48" s="3">
         <v>5900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5900</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L48" s="3">
-        <v>6400</v>
+      <c r="L48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M48" s="3">
         <v>6400</v>
       </c>
       <c r="N48" s="3">
+        <v>6400</v>
+      </c>
+      <c r="O48" s="3">
         <v>7100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2890,19 +3001,19 @@
         <v>2600</v>
       </c>
       <c r="I49" s="3">
-        <v>2800</v>
+        <v>2600</v>
       </c>
       <c r="J49" s="3">
         <v>2800</v>
       </c>
       <c r="K49" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>2800</v>
-      </c>
-      <c r="M49" s="3">
-        <v>3200</v>
       </c>
       <c r="N49" s="3">
         <v>3200</v>
@@ -2928,8 +3039,11 @@
       <c r="U49" s="3">
         <v>3200</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2987,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3046,38 +3163,41 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>9500</v>
+        <v>10200</v>
       </c>
       <c r="E52" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F52" s="3">
         <v>2500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>13800</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
@@ -3105,8 +3225,11 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3164,67 +3287,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>224200</v>
+        <v>218100</v>
       </c>
       <c r="E54" s="3">
+        <v>224700</v>
+      </c>
+      <c r="F54" s="3">
         <v>301400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>273900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>263800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>249400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>262200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>241000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>226100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>223800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>205200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>224800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>230200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>231700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>236300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>207100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>213800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>185400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>191200</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3246,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3269,8 +3399,9 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3283,12 +3414,12 @@
       <c r="F57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H57" s="3">
         <v>800</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3298,11 +3429,11 @@
       <c r="K57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M57" s="3">
         <v>2900</v>
-      </c>
-      <c r="M57" s="3">
-        <v>400</v>
       </c>
       <c r="N57" s="3">
         <v>400</v>
@@ -3311,25 +3442,28 @@
         <v>400</v>
       </c>
       <c r="P57" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q57" s="3">
         <v>5200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3337,44 +3471,44 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F58" s="3">
         <v>600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1500</v>
       </c>
-      <c r="H58" s="3">
-        <v>2000</v>
-      </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>1400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1400</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -3382,102 +3516,108 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>800</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E59" s="3">
         <v>200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>48500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3500</v>
       </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>5</v>
+      <c r="I59" s="3">
+        <v>0</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
+      <c r="K59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L59" s="3">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3">
         <v>80500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>83000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>69900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>70400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>80200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>95600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>91100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>87500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>69600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>74900</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>87600</v>
+        <v>76500</v>
       </c>
       <c r="E60" s="3">
+        <v>65500</v>
+      </c>
+      <c r="F60" s="3">
         <v>140800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>76700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>70300</v>
       </c>
-      <c r="H60" s="3">
-        <v>45200</v>
-      </c>
       <c r="I60" s="3">
+        <v>43200</v>
+      </c>
+      <c r="J60" s="3">
         <v>86900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>74700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>76700</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -3505,8 +3645,11 @@
       <c r="U60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3514,26 +3657,26 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F61" s="3">
         <v>4800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3600</v>
       </c>
-      <c r="H61" s="3">
-        <v>3200</v>
-      </c>
       <c r="I61" s="3">
+        <v>5100</v>
+      </c>
+      <c r="J61" s="3">
         <v>4800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4600</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3541,22 +3684,22 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>33700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>50900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>51000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>52100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>52200</v>
-      </c>
-      <c r="S61" s="3">
-        <v>24200</v>
       </c>
       <c r="T61" s="3">
         <v>24200</v>
@@ -3564,8 +3707,11 @@
       <c r="U61" s="3">
         <v>24200</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>24200</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3573,28 +3719,28 @@
         <v>5</v>
       </c>
       <c r="E62" s="3">
-        <v>400</v>
+        <v>19100</v>
       </c>
       <c r="F62" s="3">
         <v>400</v>
       </c>
       <c r="G62" s="3">
+        <v>400</v>
+      </c>
+      <c r="H62" s="3">
         <v>500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>20100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>300</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -3623,8 +3769,11 @@
       <c r="U62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3682,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3741,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3800,67 +3955,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>87600</v>
+        <v>76500</v>
       </c>
       <c r="E66" s="3">
+        <v>87400</v>
+      </c>
+      <c r="F66" s="3">
         <v>146100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>81400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>74500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>68500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>92100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>79600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>76700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>84800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>83800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>104700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>122800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>137800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>148100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>146000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>112100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>98500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>99400</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3882,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3941,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4000,8 +4165,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4059,8 +4227,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4118,8 +4289,11 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -4127,58 +4301,61 @@
         <v>5</v>
       </c>
       <c r="E72" s="3">
+        <v>148600</v>
+      </c>
+      <c r="F72" s="3">
         <v>132100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>551500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>542500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>527700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>512200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>500100</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M72" s="3">
         <v>471600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>451300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>442900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>426700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>410300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>400500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>371800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>409800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>394400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>399800</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4236,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4295,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4354,67 +4537,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>136600</v>
+        <v>141600</v>
       </c>
       <c r="E76" s="3">
+        <v>137300</v>
+      </c>
+      <c r="F76" s="3">
         <v>155300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>192400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>189300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>181000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>170100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>161400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>149500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>139100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>121500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>120100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>107400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>93900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>88200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>61100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>101700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>86900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>91700</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4472,131 +4661,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>15300</v>
+      </c>
+      <c r="F81" s="3">
         <v>16800</v>
       </c>
-      <c r="E81" s="3">
-        <v>16800</v>
-      </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>15000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>15800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>16600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>13100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>14600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>15900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>21400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>9400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>17300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>17500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>11000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>29200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>17100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>16000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>19700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4618,13 +4816,14 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E83" s="3">
         <v>300</v>
@@ -4654,31 +4853,34 @@
         <v>300</v>
       </c>
       <c r="N83" s="3">
+        <v>300</v>
+      </c>
+      <c r="O83" s="3">
         <v>600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>-900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>-600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4736,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4795,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4854,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4913,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4972,8 +5186,11 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4981,58 +5198,61 @@
         <v>5</v>
       </c>
       <c r="E89" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F89" s="3">
         <v>27500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>21000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>20200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-12900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>31500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>18400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>12400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>28900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>26400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>31400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-81400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>35700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>17700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>16700</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5054,8 +5274,9 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5083,8 +5304,8 @@
       <c r="K91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -5113,8 +5334,11 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5172,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5231,8 +5458,11 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5240,58 +5470,61 @@
         <v>5</v>
       </c>
       <c r="E94" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="F94" s="3">
         <v>2300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-9000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-44700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-51000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>60600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-60500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-14300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-13100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-67500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>1800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>10600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>114800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>34900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-52300</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5313,8 +5546,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5322,13 +5556,13 @@
         <v>5</v>
       </c>
       <c r="E96" s="3">
+        <v>49400</v>
+      </c>
+      <c r="F96" s="3">
         <v>1000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>5900</v>
-      </c>
-      <c r="G96" s="3">
-        <v>1000</v>
       </c>
       <c r="H96" s="3">
         <v>1000</v>
@@ -5343,37 +5577,40 @@
         <v>1000</v>
       </c>
       <c r="L96" s="3">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="M96" s="3">
         <v>-1000</v>
       </c>
       <c r="N96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="O96" s="3">
         <v>-2100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>3300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>25400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-24300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5431,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5490,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5549,8 +5792,11 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5558,58 +5804,61 @@
         <v>5</v>
       </c>
       <c r="E100" s="3">
+        <v>-84000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-3600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-11800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-7500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-6000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-43600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-26500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>42600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-28900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>27600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-24900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5667,8 +5916,11 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5676,54 +5928,57 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>-85000</v>
+      </c>
+      <c r="F102" s="3">
         <v>26200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-63400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-24000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>15900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>66900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-36100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-31400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-106400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>34400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>138400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>13000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-37800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GAMI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GAMI_QTR_FIN.xlsx
@@ -656,288 +656,301 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E8" s="3">
         <v>57300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>59300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>57500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>57600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>56900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>57300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>59500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>59200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>59900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>61600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>61900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>65600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>69600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>81700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>75900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>75600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>67900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>71300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>61300</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E9" s="3">
         <v>26600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>28800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>22600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>29000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>28600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>27300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>28200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>28100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>29200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1300</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S9" s="3">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="3">
         <v>3000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1700</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E10" s="3">
         <v>30700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>30400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>35000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>28600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>28400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>30000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>31300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>31100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>30700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>59300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>60200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>65200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>68300</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S10" s="3">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="3">
         <v>72600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>65400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>69600</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -960,8 +973,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1022,8 +1036,11 @@
       <c r="V12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,44 +1101,47 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-3400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-1600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-3300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-1600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>300</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1134,8 +1154,8 @@
       <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1146,13 +1166,16 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="E15" s="3">
         <v>200</v>
@@ -1167,7 +1190,7 @@
         <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
         <v>300</v>
@@ -1179,7 +1202,7 @@
         <v>300</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1208,8 +1231,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E17" s="3">
         <v>38700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>42100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>35900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>42000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>41600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>41300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>42000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>42700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>43500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>44600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>43900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>37300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>43700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>52200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>35200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>50800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>45500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>47700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>29400</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E18" s="3">
         <v>18600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>17100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>21600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>15700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>15300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>16000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>17500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>16500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>16400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>17000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>18000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>28300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>25900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>29500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>40700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>24800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>22400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>23600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>31900</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,23 +1410,24 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>5000</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1409,100 +1443,106 @@
       <c r="L20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>3800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-13200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>4500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-8600</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E21" s="3">
         <v>18800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>17300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>16800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>15900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>15600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>16300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>17800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>16800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>16700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>21200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>16600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>24900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>22500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>16600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>39700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>28200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>22700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>28500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>23600</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1537,10 +1577,10 @@
         <v>300</v>
       </c>
       <c r="N22" s="3">
+        <v>300</v>
+      </c>
+      <c r="O22" s="3">
         <v>600</v>
-      </c>
-      <c r="O22" s="3">
-        <v>800</v>
       </c>
       <c r="P22" s="3">
         <v>800</v>
@@ -1552,143 +1592,152 @@
         <v>800</v>
       </c>
       <c r="S22" s="3">
+        <v>800</v>
+      </c>
+      <c r="T22" s="3">
         <v>600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E23" s="3">
         <v>19800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>20600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>22700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>18200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>19700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>22000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>17800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>19800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>18300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>20600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>15600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>23500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>22600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>15400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>38600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>27300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>22700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>27500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>22600</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E24" s="3">
         <v>1500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>9500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>10200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>6700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E26" s="3">
         <v>18300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>15300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>16800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>15000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>15800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>16600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>13100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>14600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>15900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>21400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>9400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>17300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>17500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>11000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>29200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>17100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>16000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>19700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E27" s="3">
         <v>18300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>15300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>16800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>15000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>15800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>16600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>13100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>14600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>15900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>21400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>9400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>17300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>17500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>11000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>29200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>17100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>16000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>19700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1997,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,23 +2188,26 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-5000</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>5</v>
       </c>
@@ -2153,100 +2223,106 @@
       <c r="L32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>-3800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>13200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-4500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E33" s="3">
         <v>18300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>15300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>16800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>15000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>15800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>16600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>13100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>14600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>15900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>21400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>9400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>17300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>17500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>11000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>29200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>17100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>16000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>19700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E35" s="3">
         <v>18300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>15300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>16800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>15000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>15800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>16600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>13100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>14600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>15900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>21400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>9400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>17300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>17500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>11000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>29200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>17100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>16000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>19700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,81 +2570,85 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>57100</v>
+      </c>
+      <c r="E41" s="3">
         <v>53600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>17300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>102300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>76100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>65500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>61800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>125200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>149200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>133300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>66400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>102500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>133900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>144400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>142000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>152600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>118200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>118900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>33300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>20300</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>49400</v>
+      </c>
+      <c r="E42" s="3">
         <v>49900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>99200</v>
-      </c>
-      <c r="F42" s="3">
-        <v>99100</v>
       </c>
       <c r="G42" s="3">
         <v>99100</v>
@@ -2567,14 +2657,14 @@
         <v>99100</v>
       </c>
       <c r="I42" s="3">
+        <v>99100</v>
+      </c>
+      <c r="J42" s="3">
         <v>99000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>49200</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -2608,70 +2698,76 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>23100</v>
+        <v>26600</v>
       </c>
       <c r="E43" s="3">
+        <v>22100</v>
+      </c>
+      <c r="F43" s="3">
         <v>23600</v>
-      </c>
-      <c r="F43" s="3">
-        <v>21500</v>
       </c>
       <c r="G43" s="3">
         <v>21500</v>
       </c>
       <c r="H43" s="3">
+        <v>21500</v>
+      </c>
+      <c r="I43" s="3">
         <v>20800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>26200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>21400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>21500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>23000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>18600</v>
-      </c>
-      <c r="N43" s="3">
-        <v>13500</v>
       </c>
       <c r="O43" s="3">
         <v>13500</v>
       </c>
       <c r="P43" s="3">
+        <v>13500</v>
+      </c>
+      <c r="Q43" s="3">
         <v>10300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>14200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>13600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>15300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>16300</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2702,8 +2798,8 @@
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2732,8 +2828,11 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2764,8 +2863,8 @@
       <c r="L45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
+      <c r="M45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N45" s="3">
         <v>0</v>
@@ -2794,41 +2893,44 @@
       <c r="V45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>126600</v>
+        <v>133100</v>
       </c>
       <c r="E46" s="3">
+        <v>125600</v>
+      </c>
+      <c r="F46" s="3">
         <v>140000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>222900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>196700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>185400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>187000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>195700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>170700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>156300</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -2856,137 +2958,146 @@
       <c r="V46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>76400</v>
+      </c>
+      <c r="E47" s="3">
         <v>71900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>66300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>59600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>57100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>56500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>44000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>45100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>44500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>43200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>106400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>58900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>46300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>41500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>35800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>32900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>37400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>44300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>95700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>5</v>
+      <c r="D48" s="3">
+        <v>5200</v>
       </c>
       <c r="E48" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F48" s="3">
         <v>1000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5900</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M48" s="3">
-        <v>6400</v>
+      <c r="M48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N48" s="3">
         <v>6400</v>
       </c>
       <c r="O48" s="3">
+        <v>6400</v>
+      </c>
+      <c r="P48" s="3">
         <v>7100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>6700</v>
       </c>
       <c r="E49" s="3">
         <v>2600</v>
@@ -3004,19 +3115,19 @@
         <v>2600</v>
       </c>
       <c r="J49" s="3">
-        <v>2800</v>
+        <v>2600</v>
       </c>
       <c r="K49" s="3">
         <v>2800</v>
       </c>
       <c r="L49" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>2800</v>
-      </c>
-      <c r="N49" s="3">
-        <v>3200</v>
       </c>
       <c r="O49" s="3">
         <v>3200</v>
@@ -3042,8 +3153,11 @@
       <c r="V49" s="3">
         <v>3200</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,41 +3283,44 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>10200</v>
+        <v>3800</v>
       </c>
       <c r="E52" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F52" s="3">
         <v>7100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>13800</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
@@ -3228,8 +3348,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,70 +3413,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>235400</v>
+      </c>
+      <c r="E54" s="3">
         <v>218100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>224700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>301400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>273900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>263800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>249400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>262200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>241000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>226100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>223800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>205200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>224800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>230200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>231700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>236300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>207100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>213800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>185400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>191200</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,8 +3530,9 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3417,12 +3548,12 @@
       <c r="G57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I57" s="3">
         <v>800</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3432,11 +3563,11 @@
       <c r="L57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N57" s="3">
         <v>2900</v>
-      </c>
-      <c r="N57" s="3">
-        <v>400</v>
       </c>
       <c r="O57" s="3">
         <v>400</v>
@@ -3445,73 +3576,76 @@
         <v>400</v>
       </c>
       <c r="Q57" s="3">
+        <v>400</v>
+      </c>
+      <c r="R57" s="3">
         <v>5200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E58" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F58" s="3">
         <v>2200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1500</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1100</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>1400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1400</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
       <c r="S58" s="3">
         <v>0</v>
       </c>
@@ -3519,108 +3653,114 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>800</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>9900</v>
+        <v>1500</v>
       </c>
       <c r="E59" s="3">
+        <v>10200</v>
+      </c>
+      <c r="F59" s="3">
         <v>200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>48500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3500</v>
       </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>5</v>
+      <c r="J59" s="3">
+        <v>0</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
+      <c r="L59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M59" s="3">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3">
         <v>80500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>83000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>69900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>70400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>80200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>95600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>91100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>87500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>69600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>74900</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>76500</v>
+        <v>77900</v>
       </c>
       <c r="E60" s="3">
+        <v>73500</v>
+      </c>
+      <c r="F60" s="3">
         <v>65500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>140800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>76700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>70300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>43200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>86900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>74700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>76700</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -3648,38 +3788,41 @@
       <c r="V60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="E61" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F61" s="3">
         <v>2800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4600</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3687,22 +3830,22 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>33700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>50900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>51000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>52100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>52200</v>
-      </c>
-      <c r="T61" s="3">
-        <v>24200</v>
       </c>
       <c r="U61" s="3">
         <v>24200</v>
@@ -3710,40 +3853,43 @@
       <c r="V61" s="3">
         <v>24200</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>24200</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>5</v>
+      <c r="D62" s="3">
+        <v>1500</v>
       </c>
       <c r="E62" s="3">
+        <v>300</v>
+      </c>
+      <c r="F62" s="3">
         <v>19100</v>
-      </c>
-      <c r="F62" s="3">
-        <v>400</v>
       </c>
       <c r="G62" s="3">
         <v>400</v>
       </c>
       <c r="H62" s="3">
+        <v>400</v>
+      </c>
+      <c r="I62" s="3">
         <v>500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>20100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>300</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -3772,8 +3918,11 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,70 +4113,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>83000</v>
+      </c>
+      <c r="E66" s="3">
         <v>76500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>87400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>146100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>81400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>74500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>68500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>92100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>79600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>76700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>84800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>83800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>104700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>122800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>137800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>148100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>146000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>112100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>98500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>99400</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,70 +4463,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>5</v>
+      <c r="D72" s="3">
+        <v>184100</v>
       </c>
       <c r="E72" s="3">
+        <v>165100</v>
+      </c>
+      <c r="F72" s="3">
         <v>148600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>132100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>551500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>542500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>527700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>512200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>500100</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N72" s="3">
         <v>471600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>451300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>442900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>426700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>410300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>400500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>371800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>409800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>394400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>399800</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,70 +4723,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>152400</v>
+      </c>
+      <c r="E76" s="3">
         <v>141600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>137300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>155300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>192400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>189300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>181000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>170100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>161400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>149500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>139100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>121500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>120100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>107400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>93900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>88200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>61100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>101700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>86900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>91700</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E81" s="3">
         <v>18300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>15300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>16800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>15000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>15800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>16600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>13100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>14600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>15900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>21400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>9400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>17300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>17500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>11000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>29200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>17100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>16000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>19700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,8 +5015,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4826,7 +5025,7 @@
         <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
         <v>300</v>
@@ -4856,31 +5055,34 @@
         <v>300</v>
       </c>
       <c r="O83" s="3">
+        <v>300</v>
+      </c>
+      <c r="P83" s="3">
         <v>600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>-900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>-600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>5</v>
+      <c r="D89" s="3">
+        <v>11100</v>
       </c>
       <c r="E89" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F89" s="3">
         <v>3900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>27500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>21000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>20200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-12900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>31500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>18400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>12400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>28900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>26400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>31400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-81400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>35700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>17700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>16700</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,8 +5495,9 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5307,8 +5528,8 @@
       <c r="L91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -5337,8 +5558,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,70 +5688,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>5</v>
+      <c r="D94" s="3">
+        <v>-4100</v>
       </c>
       <c r="E94" s="3">
+        <v>48800</v>
+      </c>
+      <c r="F94" s="3">
         <v>-4900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>2300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-9000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-44700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-51000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>60600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-60500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-13100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-67500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>1800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>10600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>114800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>34900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-52300</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,25 +5780,26 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>5</v>
+      <c r="D96" s="3">
+        <v>1800</v>
       </c>
       <c r="E96" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F96" s="3">
         <v>49400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>5900</v>
-      </c>
-      <c r="H96" s="3">
-        <v>1000</v>
       </c>
       <c r="I96" s="3">
         <v>1000</v>
@@ -5580,37 +5814,40 @@
         <v>1000</v>
       </c>
       <c r="M96" s="3">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="N96" s="3">
         <v>-1000</v>
       </c>
       <c r="O96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="P96" s="3">
         <v>-2100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>3300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>25400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-24300</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,70 +6038,76 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>5</v>
+      <c r="D100" s="3">
+        <v>-3600</v>
       </c>
       <c r="E100" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="F100" s="3">
         <v>-84000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-11800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-6000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-43600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-26500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>42600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-12600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-28900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>27600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-24900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5919,66 +6168,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="E102" s="3">
+        <v>36300</v>
+      </c>
+      <c r="F102" s="3">
         <v>-85000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>26200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>10600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-63400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-24000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>15900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>66900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-36100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-31400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-8100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-106400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-10600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>34400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>138400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>13000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-37800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GAMI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GAMI_QTR_FIN.xlsx
@@ -3143,7 +3143,7 @@
         <v>4800</v>
       </c>
       <c r="E48" s="3">
-        <v>4500</v>
+        <v>5200</v>
       </c>
       <c r="F48" s="3">
         <v>2600</v>
@@ -3415,7 +3415,7 @@
         <v>3600</v>
       </c>
       <c r="E52" s="3">
-        <v>4500</v>
+        <v>3800</v>
       </c>
       <c r="F52" s="3">
         <v>6000</v>
